--- a/data/German_Interview_Verbs_Vocabulary - Copy.xlsx
+++ b/data/German_Interview_Verbs_Vocabulary - Copy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Deutsch\german-flashcards-architecture\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F502F1E-976D-4D46-8FA3-FD814B3FA013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C46A872D-C5CC-41B0-BA40-14A13E02DD79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Adjectives_Master" sheetId="1" r:id="rId1"/>
@@ -2684,7 +2684,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2720,6 +2720,13 @@
       <sz val="11"/>
       <color rgb="FF666666"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -2757,7 +2764,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2788,6 +2795,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2854,7 +2864,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FF666666"/>
+        <color rgb="FF1F1F1F"/>
         <name val="Calibri"/>
         <scheme val="none"/>
       </font>
@@ -2864,7 +2874,7 @@
           <bgColor rgb="FFF7FBFE"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2878,7 +2888,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
+        <color rgb="FF666666"/>
         <name val="Calibri"/>
         <scheme val="none"/>
       </font>
@@ -2888,7 +2898,7 @@
           <bgColor rgb="FFF7FBFE"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2950,8 +2960,8 @@
   <autoFilter ref="A1:E181" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="German adjective" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Meaning (simple)" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="English word" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Meaning (simple)" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="English word" dataDxfId="2"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="German example sentence" dataDxfId="1"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="English example sentence" dataDxfId="0"/>
   </tableColumns>
@@ -3245,7 +3255,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E181"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -3253,7 +3263,7 @@
     <col min="4" max="5" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3270,7 +3280,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -3287,7 +3297,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -3304,7 +3314,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -3321,7 +3331,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
@@ -3338,7 +3348,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
@@ -3355,7 +3365,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
@@ -3372,7 +3382,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
@@ -3389,7 +3399,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>14</v>
       </c>
@@ -3406,7 +3416,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>15</v>
       </c>
@@ -3423,7 +3433,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>16</v>
       </c>
@@ -3440,7 +3450,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>17</v>
       </c>
@@ -3457,7 +3467,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>18</v>
       </c>
@@ -3474,7 +3484,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>19</v>
       </c>
@@ -3491,7 +3501,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>20</v>
       </c>
@@ -3508,7 +3518,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>21</v>
       </c>
@@ -3525,7 +3535,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>22</v>
       </c>
@@ -3542,7 +3552,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>23</v>
       </c>
@@ -3559,7 +3569,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>24</v>
       </c>
@@ -3576,7 +3586,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>25</v>
       </c>
@@ -3593,7 +3603,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>26</v>
       </c>
@@ -3610,7 +3620,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>27</v>
       </c>
@@ -3627,7 +3637,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>28</v>
       </c>
@@ -3644,7 +3654,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>29</v>
       </c>
@@ -3661,7 +3671,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>30</v>
       </c>
@@ -3678,7 +3688,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>31</v>
       </c>
@@ -3695,7 +3705,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>32</v>
       </c>
@@ -3712,7 +3722,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>33</v>
       </c>
@@ -3729,7 +3739,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>34</v>
       </c>
@@ -3746,7 +3756,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>35</v>
       </c>
@@ -3763,7 +3773,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>36</v>
       </c>
@@ -3780,7 +3790,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>37</v>
       </c>
@@ -3797,7 +3807,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>38</v>
       </c>
@@ -3814,7 +3824,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>39</v>
       </c>
@@ -3831,7 +3841,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>40</v>
       </c>
@@ -3848,7 +3858,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
         <v>41</v>
       </c>
@@ -3865,7 +3875,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>42</v>
       </c>
@@ -3882,7 +3892,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
         <v>43</v>
       </c>
@@ -3899,7 +3909,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>44</v>
       </c>
@@ -3916,7 +3926,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
         <v>45</v>
       </c>
@@ -3933,7 +3943,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>46</v>
       </c>
@@ -3950,7 +3960,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>47</v>
       </c>
@@ -3967,7 +3977,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>48</v>
       </c>
@@ -3984,7 +3994,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>49</v>
       </c>
@@ -4001,7 +4011,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>50</v>
       </c>
@@ -4018,7 +4028,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>51</v>
       </c>
@@ -4035,7 +4045,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>52</v>
       </c>
@@ -4052,7 +4062,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>53</v>
       </c>
@@ -4069,7 +4079,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>54</v>
       </c>
@@ -4086,7 +4096,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>55</v>
       </c>
@@ -4103,7 +4113,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>56</v>
       </c>
@@ -4120,7 +4130,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>57</v>
       </c>
@@ -4137,7 +4147,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>58</v>
       </c>
@@ -4154,7 +4164,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
         <v>59</v>
       </c>
@@ -4171,7 +4181,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
         <v>60</v>
       </c>
@@ -4188,7 +4198,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>61</v>
       </c>
@@ -4205,7 +4215,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>62</v>
       </c>
@@ -4222,7 +4232,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
         <v>63</v>
       </c>
@@ -4239,7 +4249,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
         <v>64</v>
       </c>
@@ -4256,7 +4266,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>65</v>
       </c>
@@ -4273,7 +4283,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
         <v>66</v>
       </c>
@@ -4290,7 +4300,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
         <v>67</v>
       </c>
@@ -4307,7 +4317,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
         <v>68</v>
       </c>
@@ -4324,7 +4334,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
         <v>69</v>
       </c>
@@ -4341,7 +4351,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
         <v>70</v>
       </c>
@@ -4358,7 +4368,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
         <v>71</v>
       </c>
@@ -4375,7 +4385,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
         <v>72</v>
       </c>
@@ -4392,7 +4402,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
         <v>73</v>
       </c>
@@ -4409,7 +4419,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
         <v>74</v>
       </c>
@@ -4426,7 +4436,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
         <v>75</v>
       </c>
@@ -4443,7 +4453,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
         <v>76</v>
       </c>
@@ -4460,7 +4470,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
         <v>77</v>
       </c>
@@ -4477,7 +4487,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
         <v>78</v>
       </c>
@@ -4494,7 +4504,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
         <v>79</v>
       </c>
@@ -4511,7 +4521,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="s">
         <v>80</v>
       </c>
@@ -4528,7 +4538,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="3" t="s">
         <v>81</v>
       </c>
@@ -4545,7 +4555,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="3" t="s">
         <v>82</v>
       </c>
@@ -4562,7 +4572,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="3" t="s">
         <v>83</v>
       </c>
@@ -4579,7 +4589,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="3" t="s">
         <v>84</v>
       </c>
@@ -4596,7 +4606,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="3" t="s">
         <v>85</v>
       </c>
@@ -4613,7 +4623,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="3" t="s">
         <v>86</v>
       </c>
@@ -4630,7 +4640,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="3" t="s">
         <v>87</v>
       </c>
@@ -4647,7 +4657,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="3" t="s">
         <v>88</v>
       </c>
@@ -4664,7 +4674,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="3" t="s">
         <v>89</v>
       </c>
@@ -4681,7 +4691,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" s="3" t="s">
         <v>90</v>
       </c>
@@ -4698,7 +4708,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A86" s="3" t="s">
         <v>91</v>
       </c>
@@ -4715,7 +4725,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" s="3" t="s">
         <v>92</v>
       </c>
@@ -4732,7 +4742,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" s="3" t="s">
         <v>93</v>
       </c>
@@ -4749,7 +4759,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
         <v>94</v>
       </c>
@@ -4766,7 +4776,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" s="3" t="s">
         <v>95</v>
       </c>
@@ -4783,7 +4793,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" s="3" t="s">
         <v>96</v>
       </c>
@@ -4800,7 +4810,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" s="3" t="s">
         <v>95</v>
       </c>
@@ -4817,7 +4827,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="3" t="s">
         <v>97</v>
       </c>
@@ -4834,7 +4844,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" s="3" t="s">
         <v>98</v>
       </c>
@@ -4851,7 +4861,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="3" t="s">
         <v>99</v>
       </c>
@@ -4868,7 +4878,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" s="3" t="s">
         <v>93</v>
       </c>
@@ -4885,7 +4895,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
         <v>100</v>
       </c>
@@ -4902,7 +4912,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
         <v>101</v>
       </c>
@@ -4919,7 +4929,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
         <v>102</v>
       </c>
@@ -4936,7 +4946,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
         <v>103</v>
       </c>
@@ -4953,7 +4963,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
         <v>104</v>
       </c>
@@ -4970,7 +4980,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
         <v>105</v>
       </c>
@@ -4987,7 +4997,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
         <v>106</v>
       </c>
@@ -5004,7 +5014,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
         <v>107</v>
       </c>
@@ -5021,7 +5031,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
         <v>108</v>
       </c>
@@ -5038,7 +5048,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
         <v>109</v>
       </c>
@@ -5055,7 +5065,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
         <v>110</v>
       </c>
@@ -5072,7 +5082,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
         <v>111</v>
       </c>
@@ -5089,7 +5099,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
         <v>112</v>
       </c>
@@ -5106,7 +5116,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
         <v>113</v>
       </c>
@@ -5123,7 +5133,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
         <v>114</v>
       </c>
@@ -5140,7 +5150,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
         <v>115</v>
       </c>
@@ -5157,7 +5167,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
         <v>116</v>
       </c>
@@ -5174,7 +5184,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
         <v>117</v>
       </c>
@@ -5191,7 +5201,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
         <v>118</v>
       </c>
@@ -5208,7 +5218,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
         <v>119</v>
       </c>
@@ -5225,7 +5235,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
         <v>120</v>
       </c>
@@ -5242,7 +5252,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
         <v>121</v>
       </c>
@@ -5259,7 +5269,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
         <v>122</v>
       </c>
@@ -5276,7 +5286,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
         <v>123</v>
       </c>
@@ -5293,7 +5303,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
         <v>124</v>
       </c>
@@ -5310,7 +5320,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
         <v>125</v>
       </c>
@@ -5327,7 +5337,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
         <v>126</v>
       </c>
@@ -5344,7 +5354,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
         <v>127</v>
       </c>
@@ -5361,7 +5371,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
         <v>128</v>
       </c>
@@ -5378,7 +5388,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
         <v>129</v>
       </c>
@@ -5395,7 +5405,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" s="3" t="s">
         <v>130</v>
       </c>
@@ -5412,7 +5422,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" s="3" t="s">
         <v>131</v>
       </c>
@@ -5429,7 +5439,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" s="3" t="s">
         <v>132</v>
       </c>
@@ -5446,7 +5456,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" s="3" t="s">
         <v>133</v>
       </c>
@@ -5463,7 +5473,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" s="3" t="s">
         <v>134</v>
       </c>
@@ -5480,7 +5490,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" s="3" t="s">
         <v>135</v>
       </c>
@@ -5497,7 +5507,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" s="3" t="s">
         <v>136</v>
       </c>
@@ -5514,7 +5524,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" s="3" t="s">
         <v>137</v>
       </c>
@@ -5531,7 +5541,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" s="3" t="s">
         <v>138</v>
       </c>
@@ -5548,7 +5558,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" s="3" t="s">
         <v>139</v>
       </c>
@@ -5565,7 +5575,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" s="3" t="s">
         <v>140</v>
       </c>
@@ -5582,7 +5592,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" s="3" t="s">
         <v>141</v>
       </c>
@@ -5599,7 +5609,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" s="3" t="s">
         <v>142</v>
       </c>
@@ -5616,7 +5626,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" s="3" t="s">
         <v>143</v>
       </c>
@@ -5633,7 +5643,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" s="3" t="s">
         <v>144</v>
       </c>
@@ -5650,7 +5660,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" s="3" t="s">
         <v>145</v>
       </c>
@@ -5667,7 +5677,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" s="3" t="s">
         <v>46</v>
       </c>
@@ -5684,7 +5694,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" s="3" t="s">
         <v>146</v>
       </c>
@@ -5701,7 +5711,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" s="3" t="s">
         <v>147</v>
       </c>
@@ -5718,7 +5728,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A146" s="3" t="s">
         <v>148</v>
       </c>
@@ -5735,7 +5745,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" s="3" t="s">
         <v>149</v>
       </c>
@@ -5752,8 +5762,8 @@
         <v>851</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A148" s="3" t="s">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A148" s="11" t="s">
         <v>150</v>
       </c>
       <c r="B148" s="7" t="s">
@@ -5769,7 +5779,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A149" s="3" t="s">
         <v>151</v>
       </c>
@@ -5786,7 +5796,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" s="3" t="s">
         <v>152</v>
       </c>
@@ -5803,7 +5813,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" s="3" t="s">
         <v>153</v>
       </c>
@@ -5820,7 +5830,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" s="3" t="s">
         <v>154</v>
       </c>
@@ -5837,7 +5847,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" s="3" t="s">
         <v>155</v>
       </c>
@@ -5854,7 +5864,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" s="3" t="s">
         <v>156</v>
       </c>
@@ -5871,7 +5881,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" s="3" t="s">
         <v>157</v>
       </c>
@@ -5888,7 +5898,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" s="3" t="s">
         <v>158</v>
       </c>
@@ -5905,7 +5915,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
         <v>40</v>
       </c>
@@ -5922,7 +5932,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
         <v>159</v>
       </c>
@@ -5939,7 +5949,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
         <v>160</v>
       </c>
@@ -5956,7 +5966,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
         <v>161</v>
       </c>
@@ -5973,7 +5983,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
         <v>162</v>
       </c>
@@ -5990,7 +6000,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
         <v>47</v>
       </c>
@@ -6007,7 +6017,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
         <v>13</v>
       </c>
@@ -6024,7 +6034,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
         <v>163</v>
       </c>
@@ -6041,7 +6051,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
         <v>164</v>
       </c>
@@ -6058,7 +6068,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
         <v>57</v>
       </c>
@@ -6075,7 +6085,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
         <v>165</v>
       </c>
@@ -6092,7 +6102,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
         <v>166</v>
       </c>
@@ -6109,7 +6119,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
         <v>167</v>
       </c>
@@ -6126,7 +6136,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
         <v>168</v>
       </c>
@@ -6143,7 +6153,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
         <v>169</v>
       </c>
@@ -6160,7 +6170,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
         <v>170</v>
       </c>
@@ -6177,7 +6187,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
         <v>171</v>
       </c>
@@ -6194,7 +6204,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
         <v>172</v>
       </c>
@@ -6211,7 +6221,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
         <v>173</v>
       </c>
@@ -6228,7 +6238,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
         <v>87</v>
       </c>
@@ -6245,7 +6255,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
         <v>174</v>
       </c>
@@ -6262,7 +6272,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
         <v>175</v>
       </c>
@@ -6279,7 +6289,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
         <v>176</v>
       </c>
@@ -6296,7 +6306,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
         <v>177</v>
       </c>
@@ -6313,7 +6323,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="181" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
         <v>178</v>
       </c>
